--- a/trajectory_exports/test_basic.xlsx
+++ b/trajectory_exports/test_basic.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-18T20:18:15.530086+00:00</t>
+          <t>2026-08-26T15:41:36.509268+00:00</t>
         </is>
       </c>
     </row>

--- a/trajectory_exports/test_basic.xlsx
+++ b/trajectory_exports/test_basic.xlsx
@@ -800,7 +800,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26T15:41:36.509268+00:00</t>
+          <t>2026-09-01T17:26:51.932463+00:00</t>
         </is>
       </c>
     </row>
